--- a/data/trans_orig/IP04D$colectiva-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131493</t>
+          <t>131067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137719</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149101</t>
+          <t>148839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154065</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283026</t>
+          <t>283230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291094</t>
+          <t>290941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189643</t>
+          <t>188969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>199726</t>
+          <t>199335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211110</t>
+          <t>210983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219864</t>
+          <t>219874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404464</t>
+          <t>404041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417473</t>
+          <t>417040</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150149</t>
+          <t>149820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158633</t>
+          <t>158900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164643</t>
+          <t>164644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312289</t>
+          <t>312503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318883</t>
+          <t>319106</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>28704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>192808</t>
+          <t>193223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203250</t>
+          <t>203776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192116</t>
+          <t>192326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203870</t>
+          <t>203768</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389312</t>
+          <t>389202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405322</t>
+          <t>405100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673894</t>
+          <t>675357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>690310</t>
+          <t>690852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>722190</t>
+          <t>723178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737217</t>
+          <t>737948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1403167</t>
+          <t>1402404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1424615</t>
+          <t>1425888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123854</t>
+          <t>124113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131370</t>
+          <t>131414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141907</t>
+          <t>141892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147319</t>
+          <t>147322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269674</t>
+          <t>268973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278016</t>
+          <t>277890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197036</t>
+          <t>196884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204071</t>
+          <t>204097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>215957</t>
+          <t>215668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222345</t>
+          <t>222365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416084</t>
+          <t>415167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425385</t>
+          <t>424907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,47 +3380,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8456</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148192</t>
+          <t>148588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154683</t>
+          <t>154166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,49 +3493,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>162342</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>157863</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>164513</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>162342</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>157458</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164572</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,9%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>494</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308845</t>
+          <t>309320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318001</t>
+          <t>318046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>23713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>19856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>37427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186426</t>
+          <t>187295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198252</t>
+          <t>198355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177701</t>
+          <t>178620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191314</t>
+          <t>191548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369109</t>
+          <t>370238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386901</t>
+          <t>387809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>666314</t>
+          <t>665729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>682789</t>
+          <t>682158</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>704301</t>
+          <t>704642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720629</t>
+          <t>721497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376083</t>
+          <t>1376526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400081</t>
+          <t>1400092</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>25329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99203</t>
+          <t>98559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>108642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130474</t>
+          <t>129708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137480</t>
+          <t>137506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232007</t>
+          <t>232364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244919</t>
+          <t>245024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42913</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167224</t>
+          <t>167974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180322</t>
+          <t>180256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228979</t>
+          <t>228719</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242266</t>
+          <t>242202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>400928</t>
+          <t>402180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419631</t>
+          <t>419594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>30973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173523</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185386</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167900</t>
+          <t>167679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179919</t>
+          <t>179596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346425</t>
+          <t>344714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362504</t>
+          <t>361490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44287</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146728</t>
+          <t>147222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158359</t>
+          <t>158880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151469</t>
+          <t>153283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167675</t>
+          <t>167334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303970</t>
+          <t>304865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>323328</t>
+          <t>324161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64809</t>
+          <t>64200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>65804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87935</t>
+          <t>89985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122650</t>
+          <t>122939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>600347</t>
+          <t>600956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>623672</t>
+          <t>624125</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694359</t>
+          <t>694518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718019</t>
+          <t>719246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302827</t>
+          <t>1302538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1337542</t>
+          <t>1335492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$colectiva-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5629</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2874</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6765</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2096</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5845</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152588</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149055</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>154055</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135514</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>131067</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137708</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131623</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137705</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152588</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148839</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>154053</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283230</t>
+          <t>283280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290941</t>
+          <t>291099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12374</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9888</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5684</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16050</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15840</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7406</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12852</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>211461</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219873</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>195131</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>188969</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>199335</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>189179</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>199107</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>216429</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>210983</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>219874</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404041</t>
+          <t>404122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417040</t>
+          <t>416776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2518</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1462</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5556</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2518</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6410</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8183</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162792</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159087</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164640</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,24%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153914</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149820</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150154</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>162792</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>158900</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164644</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>490</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312503</t>
+          <t>312179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319106</t>
+          <t>319136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8952</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15730</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10578</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5734</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16287</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5895</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17268</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8952</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4628</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16070</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>29081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199444</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192666</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>203655</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>198932</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>193223</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>203776</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>192242</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>203615</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199444</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192326</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>203768</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389202</t>
+          <t>388825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405100</t>
+          <t>404631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14210</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29957</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17440</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32935</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18213</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33912</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>45774</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>35876</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>58667</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14277</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29047</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>45774</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>34629</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>58113</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -2207,107 +2207,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>731253</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>722268</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>738015</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>986</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>683490</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>675357</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>690852</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>674380</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>690079</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1414743</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1401850</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1424641</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>731253</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>723178</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>737948</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1414743</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1402404</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1425888</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4314</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8759</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8803</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2326</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6184</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>145750</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>141798</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>147315</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128558</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124113</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131414</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>124069</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131400</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>145750</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141892</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>147322</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>268973</t>
+          <t>269097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277890</t>
+          <t>278042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3686</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8755</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4484</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9095</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8626</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3686</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8020</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220002</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>214933</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>222248</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>201495</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>196884</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>204097</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>197353</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>204085</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220002</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>215668</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>222365</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415167</t>
+          <t>415045</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>424907</t>
+          <t>424899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,67 +3360,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>3827</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7409</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8051</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162342</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>157907</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164477</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152170</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148588</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154166</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>147835</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154652</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>162342</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>157863</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>164513</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309320</t>
+          <t>309115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318046</t>
+          <t>317901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16624</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10825</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23940</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11651</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6977</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18037</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6727</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18118</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16624</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10785</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>23713</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>185709</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>178393</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191508</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>193681</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>187295</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>198355</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>187214</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>198605</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>185709</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>178620</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>191548</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>370238</t>
+          <t>370266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387809</t>
+          <t>387537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19093</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35833</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18023</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34452</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17194</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>32882</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18514</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35369</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -4159,67 +4159,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>713803</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>704178</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>720918</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>675905</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>665729</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>682158</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>667299</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>682987</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>713803</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>704642</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721497</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1376526</t>
+          <t>1377869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400092</t>
+          <t>1401378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4853</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8803</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12596</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18721</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121053</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>117103</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123377</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>104684</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>98559</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>108642</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134865</t>
+          <t>108404</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129708</t>
+          <t>102190</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137506</t>
+          <t>112863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>239550</t>
+          <t>229457</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232364</t>
+          <t>223162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245024</t>
+          <t>234703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15177</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9943</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22369</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14952</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9257</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21539</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32687</t>
+          <t>30282</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41661</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221413</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>214221</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>226647</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>174561</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>167974</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>180256</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>236593</t>
+          <t>168233</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228719</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242202</t>
+          <t>173929</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>411154</t>
+          <t>389645</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402180</t>
+          <t>380209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419594</t>
+          <t>397729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9529</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15989</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10409</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5562</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17172</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10977</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6387</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18937</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>20506</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>13661</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>29365</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>9,02%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10069</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5690</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17607</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>20478</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>14197</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>30973</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -5415,107 +5415,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158812</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>152352</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>163438</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>179992</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>173229</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>184839</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>146073</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138113</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150663</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>304885</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>296026</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>311730</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>90,98%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>175217</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>167679</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>179596</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>355209</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>344714</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>361490</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>91,76%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17991</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25402</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14168</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9082</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20740</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>20594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>23954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>42256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150428</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143017</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>156150</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>153794</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>147222</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158880</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>160883</t>
+          <t>152970</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153283</t>
+          <t>146551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167334</t>
+          <t>158078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>314677</t>
+          <t>303397</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304865</t>
+          <t>293308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324161</t>
+          <t>311610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37489</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>59236</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41031</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>64200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>66630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89985</t>
+          <t>85194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>122939</t>
+          <t>115246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>651705</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>640020</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>661767</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>860</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>613031</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>600956</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>624125</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>92,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>707559</t>
+          <t>575679</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>694518</t>
+          <t>561973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719246</t>
+          <t>585739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1320589</t>
+          <t>1227384</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1302538</t>
+          <t>1212613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1335492</t>
+          <t>1242665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
